--- a/src/test/resources/TEST_DATA/SavingsandFDData.xlsx
+++ b/src/test/resources/TEST_DATA/SavingsandFDData.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="51"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="44"/>
   </bookViews>
   <sheets>
     <sheet name="LoginData" sheetId="1" state="visible" r:id="rId1"/>
@@ -717,7 +717,7 @@
     <t>1000.00</t>
   </si>
   <si>
-    <t>TestUser100</t>
+    <t>TestUser10</t>
   </si>
   <si>
     <t>shirania</t>
@@ -1160,7 +1160,7 @@
     <t>25238.36</t>
   </si>
   <si>
-    <t>TestUser101</t>
+    <t>TestUser11</t>
   </si>
   <si>
     <t>minimumAmount</t>
@@ -1389,7 +1389,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1">
       <protection hidden="0" locked="1"/>
@@ -1466,7 +1466,6 @@
     <xf fontId="3" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4005,6 +4004,12 @@
 <file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="37.7109375"/>
+    <col customWidth="1" min="2" max="2" width="17.57421875"/>
+    <col customWidth="1" min="3" max="3" width="30.57421875"/>
+    <col bestFit="1" min="10" max="10" width="9.28125"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
@@ -4076,7 +4081,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="3" ht="71.25">
+    <row r="3" ht="42.75">
       <c r="A3" s="5" t="s">
         <v>355</v>
       </c>
@@ -5652,7 +5657,7 @@
       <c r="D2" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E2" s="27" t="s">
+      <c r="E2" s="5" t="s">
         <v>410</v>
       </c>
       <c r="F2" s="5" t="s">

--- a/src/test/resources/TEST_DATA/SavingsandFDData.xlsx
+++ b/src/test/resources/TEST_DATA/SavingsandFDData.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="44"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="43"/>
   </bookViews>
   <sheets>
     <sheet name="LoginData" sheetId="1" state="visible" r:id="rId1"/>
@@ -51,13 +51,14 @@
     <sheet name="LoginDataAlternateFive" sheetId="43" state="visible" r:id="rId43"/>
     <sheet name="SavingsAccountNumber" sheetId="44" state="visible" r:id="rId44"/>
     <sheet name="FDCompleteFlowData" sheetId="45" state="visible" r:id="rId45"/>
-    <sheet name="PawningData" sheetId="46" state="visible" r:id="rId46"/>
-    <sheet name="LoanDetails" sheetId="47" state="visible" r:id="rId47"/>
-    <sheet name="SADetailedViewData" sheetId="48" state="visible" r:id="rId48"/>
-    <sheet name="CADetailedViewData" sheetId="49" state="visible" r:id="rId49"/>
-    <sheet name="ChequeRequestData" sheetId="50" state="visible" r:id="rId50"/>
-    <sheet name="AdvancedSearchData" sheetId="51" state="visible" r:id="rId51"/>
-    <sheet name="AcknowledgementMessages" sheetId="52" state="visible" r:id="rId52"/>
+    <sheet name="SavingSuccessMsg" sheetId="46" state="visible" r:id="rId46"/>
+    <sheet name="PawningData" sheetId="47" state="visible" r:id="rId47"/>
+    <sheet name="LoanDetails" sheetId="48" state="visible" r:id="rId48"/>
+    <sheet name="SADetailedViewData" sheetId="49" state="visible" r:id="rId49"/>
+    <sheet name="CADetailedViewData" sheetId="50" state="visible" r:id="rId50"/>
+    <sheet name="ChequeRequestData" sheetId="51" state="visible" r:id="rId51"/>
+    <sheet name="AdvancedSearchData" sheetId="52" state="visible" r:id="rId52"/>
+    <sheet name="AcknowledgementMessages" sheetId="53" state="visible" r:id="rId53"/>
   </sheets>
   <calcPr/>
   <extLst>
@@ -67,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="420">
   <si>
     <t>userName</t>
   </si>
@@ -1106,6 +1107,9 @@
     <t xml:space="preserve">SMS sent successfully to the registered mobile number:******9261</t>
   </si>
   <si>
+    <t>101050126359</t>
+  </si>
+  <si>
     <t>product</t>
   </si>
   <si>
@@ -1136,6 +1140,12 @@
     <t>100000.00</t>
   </si>
   <si>
+    <t>4010.96</t>
+  </si>
+  <si>
+    <t>104010.96</t>
+  </si>
+  <si>
     <t>fahimmohamed </t>
   </si>
   <si>
@@ -1154,13 +1164,22 @@
     <t>25000.00</t>
   </si>
   <si>
-    <t>238.36</t>
-  </si>
-  <si>
-    <t>25238.36</t>
+    <t>246.58</t>
+  </si>
+  <si>
+    <t>25246.58</t>
   </si>
   <si>
     <t>TestUser11</t>
+  </si>
+  <si>
+    <t>suffixMsg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your new savings account</t>
+  </si>
+  <si>
+    <t xml:space="preserve">has been successfully created</t>
   </si>
   <si>
     <t>minimumAmount</t>
@@ -1389,7 +1408,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1">
       <protection hidden="0" locked="1"/>
@@ -1454,6 +1473,7 @@
     <xf fontId="7" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1"/>
     <xf fontId="9" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -3989,8 +4009,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>218</v>
+      <c r="A2" s="23" t="s">
+        <v>345</v>
       </c>
     </row>
   </sheetData>
@@ -4022,25 +4042,25 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>214</v>
@@ -4051,31 +4071,31 @@
         <v>217</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>344</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>218</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>354</v>
-      </c>
-      <c r="I2" s="5">
-        <v>3989.04</v>
-      </c>
-      <c r="J2" s="5">
-        <v>103989.03999999999</v>
+        <v>355</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>357</v>
       </c>
       <c r="K2" s="5" t="s">
         <v>216</v>
@@ -4083,37 +4103,37 @@
     </row>
     <row r="3" ht="42.75">
       <c r="A3" s="5" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="C3" s="23" t="s">
+        <v>351</v>
+      </c>
+      <c r="C3" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="24" t="s">
-        <v>356</v>
+      <c r="D3" s="25" t="s">
+        <v>359</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
   </sheetData>
@@ -4126,49 +4146,25 @@
 
 <file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="16384" style="5" width="9.140625"/>
+    <col customWidth="1" min="1" max="1" width="37.57421875"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="25" t="s">
-        <v>364</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="A1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B1" t="s">
         <v>367</v>
       </c>
-      <c r="E1" s="2" t="s">
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
         <v>368</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="s">
+      <c r="B2" t="s">
         <v>369</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>370</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>371</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>373</v>
       </c>
     </row>
   </sheetData>
@@ -4181,6 +4177,61 @@
 
 <file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="16384" style="5" width="9.140625"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="26" t="s">
+        <v>370</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>379</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="6" style="5" width="9.140625"/>
@@ -4190,54 +4241,54 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="B1" s="26" t="s">
+        <v>370</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>374</v>
-      </c>
-      <c r="B1" s="25" t="s">
-        <v>364</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>368</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>376</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>369</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>370</v>
-      </c>
       <c r="D2" s="5" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>195</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
     </row>
   </sheetData>
@@ -4248,7 +4299,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -4268,121 +4319,57 @@
         <v>17</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>388</v>
-      </c>
-      <c r="H2" s="26" t="s">
-        <v>392</v>
+        <v>394</v>
+      </c>
+      <c r="H2" s="27" t="s">
+        <v>398</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>392</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="5" style="5" width="9.140625"/>
-    <col bestFit="1" min="6" max="6" style="5" width="14.140625"/>
-    <col bestFit="1" min="7" max="7" style="5" width="9.8515625"/>
-    <col min="8" max="16384" style="5" width="9.140625"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>393</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>394</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>395</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>396</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>382</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="B2" s="5" t="s">
         <v>398</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>388</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>399</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>388</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>400</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>401</v>
       </c>
     </row>
   </sheetData>
@@ -5513,17 +5500,56 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="16384" style="5" width="9.140625"/>
+    <col min="1" max="5" style="5" width="9.140625"/>
+    <col bestFit="1" min="6" max="6" style="5" width="14.140625"/>
+    <col bestFit="1" min="7" max="7" style="5" width="9.8515625"/>
+    <col min="8" max="16384" style="5" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="27" t="s">
         <v>17</v>
       </c>
+      <c r="B1" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>401</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>402</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>403</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="5" t="s">
         <v>241</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>407</v>
       </c>
     </row>
   </sheetData>
@@ -5536,67 +5562,20 @@
 
 <file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" min="1" max="1" style="5" width="18.8515625"/>
-    <col min="2" max="16384" style="5" width="9.140625"/>
+    <col min="1" max="16384" style="5" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>346</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>402</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>403</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>404</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>405</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>384</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>385</v>
-      </c>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="27" t="s">
         <v>241</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>406</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>407</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>407</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>390</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>408</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>408</v>
-      </c>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -5607,6 +5586,78 @@
 </file>
 
 <file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" style="5" width="18.8515625"/>
+    <col min="2" max="16384" style="5" width="9.140625"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>408</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>409</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>410</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>411</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>391</v>
+      </c>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>412</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>413</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>413</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+    </row>
+  </sheetData>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -5634,14 +5685,14 @@
       <c r="E1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="27" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>16</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
     </row>
     <row r="2">
@@ -5658,16 +5709,16 @@
         <v>39</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
     </row>
   </sheetData>
